--- a/shocks_web.xlsx
+++ b/shocks_web.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27" uniqueCount="15">
   <si>
     <t>by Mark Kerssenfischer</t>
   </si>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" style="2" customWidth="true"/>
@@ -587,10 +587,10 @@
         <v>-0.015398232202659137</v>
       </c>
       <c r="C2" s="10">
-        <v>-0.21094150343983395</v>
+        <v>-0.20852523879293078</v>
       </c>
       <c r="D2" s="10">
-        <v>-0.21384435402516594</v>
+        <v>-0.21643286859390035</v>
       </c>
     </row>
     <row r="3">
@@ -601,10 +601,10 @@
         <v>0.0050065878184445967</v>
       </c>
       <c r="C3" s="10">
-        <v>-0.29488730187710172</v>
+        <v>-0.29347927128409257</v>
       </c>
       <c r="D3" s="10">
-        <v>0.56037718637679534</v>
+        <v>0.56577421104470726</v>
       </c>
     </row>
     <row r="4">
@@ -615,10 +615,10 @@
         <v>0.051663768913218409</v>
       </c>
       <c r="C4" s="10">
-        <v>0.75584697713054738</v>
+        <v>0.76632475932209443</v>
       </c>
       <c r="D4" s="10">
-        <v>0.71389129762365244</v>
+        <v>0.72274812820525003</v>
       </c>
     </row>
     <row r="5">
@@ -629,10 +629,10 @@
         <v>0.035650828790285541</v>
       </c>
       <c r="C5" s="10">
-        <v>0.69039943035841111</v>
+        <v>0.70046632551963084</v>
       </c>
       <c r="D5" s="10">
-        <v>0.27717273454764929</v>
+        <v>0.28132682936634318</v>
       </c>
     </row>
     <row r="6">
@@ -643,10 +643,10 @@
         <v>-0.0099549776677726291</v>
       </c>
       <c r="C6" s="10">
-        <v>-0.19759770583290065</v>
+        <v>-0.19512327074419775</v>
       </c>
       <c r="D6" s="10">
-        <v>-0.053807056312789064</v>
+        <v>-0.05469093847861977</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         <v>-0</v>
       </c>
       <c r="C7" s="10">
-        <v>0.34430294506908232</v>
+        <v>0.35162077951886511</v>
       </c>
       <c r="D7" s="10">
-        <v>-0.4344137147865178</v>
+        <v>-0.4383431847828595</v>
       </c>
     </row>
     <row r="8">
@@ -671,10 +671,10 @@
         <v>-0.038427182140449344</v>
       </c>
       <c r="C8" s="10">
-        <v>8.9312723106917736e-06</v>
+        <v>0.0046268349034391861</v>
       </c>
       <c r="D8" s="10">
-        <v>-1.238828012257178</v>
+        <v>-1.2518130248492889</v>
       </c>
     </row>
     <row r="9">
@@ -685,10 +685,10 @@
         <v>0.01247752452095988</v>
       </c>
       <c r="C9" s="10">
-        <v>0.14879689886085198</v>
+        <v>0.15417847909040458</v>
       </c>
       <c r="D9" s="10">
-        <v>0.22659972580351137</v>
+        <v>0.22927043694184526</v>
       </c>
     </row>
     <row r="10">
@@ -699,10 +699,10 @@
         <v>-0.016854568634729762</v>
       </c>
       <c r="C10" s="10">
-        <v>0.49569969012570264</v>
+        <v>0.50460145868665807</v>
       </c>
       <c r="D10" s="10">
-        <v>-1.1806884170205096</v>
+        <v>-1.1921912711723099</v>
       </c>
     </row>
     <row r="11">
@@ -713,10 +713,10 @@
         <v>0.022672179504226508</v>
       </c>
       <c r="C11" s="10">
-        <v>-0.0016525652626449045</v>
+        <v>0.0022320262258843592</v>
       </c>
       <c r="D11" s="10">
-        <v>0.75459208311856207</v>
+        <v>0.76254481136498564</v>
       </c>
     </row>
     <row r="12">
@@ -727,10 +727,10 @@
         <v>0.013636734138774415</v>
       </c>
       <c r="C12" s="10">
-        <v>-0.56361546067280333</v>
+        <v>-0.56476871978498944</v>
       </c>
       <c r="D12" s="10">
-        <v>1.1912689020469964</v>
+        <v>1.2028209602962683</v>
       </c>
     </row>
     <row r="13">
@@ -741,10 +741,10 @@
         <v>0.010717942484731867</v>
       </c>
       <c r="C13" s="10">
-        <v>0.78652154443560818</v>
+        <v>0.79776135064284248</v>
       </c>
       <c r="D13" s="10">
-        <v>-0.66046281950647678</v>
+        <v>-0.66598950482893537</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>-0.047625986463875253</v>
       </c>
       <c r="C14" s="10">
-        <v>0.47332265484976982</v>
+        <v>0.48238124827954409</v>
       </c>
       <c r="D14" s="10">
-        <v>-2.1544303056172383</v>
+        <v>-2.1762015507025034</v>
       </c>
     </row>
     <row r="15">
@@ -769,10 +769,10 @@
         <v>-0.0048531129021494781</v>
       </c>
       <c r="C15" s="10">
-        <v>0.11140699314378784</v>
+        <v>0.11665000476179703</v>
       </c>
       <c r="D15" s="10">
-        <v>-0.2895678682439834</v>
+        <v>-0.29238517188940721</v>
       </c>
     </row>
     <row r="16">
@@ -783,10 +783,10 @@
         <v>0.050065942976854731</v>
       </c>
       <c r="C16" s="10">
-        <v>1.3788670112193355</v>
+        <v>1.3950665165347031</v>
       </c>
       <c r="D16" s="10">
-        <v>-0.14876798069154665</v>
+        <v>-0.14787804313105612</v>
       </c>
     </row>
     <row r="17">
@@ -797,10 +797,10 @@
         <v>-0.063473123670821557</v>
       </c>
       <c r="C17" s="10">
-        <v>-0.61867191821420353</v>
+        <v>-0.61942287279079178</v>
       </c>
       <c r="D17" s="10">
-        <v>-1.2501478150069121</v>
+        <v>-1.2643393617990433</v>
       </c>
     </row>
     <row r="18">
@@ -811,10 +811,10 @@
         <v>0.0021812212757780633</v>
       </c>
       <c r="C18" s="10">
-        <v>-0.13641883576777941</v>
+        <v>-0.13352702437412173</v>
       </c>
       <c r="D18" s="10">
-        <v>0.26212039277166266</v>
+        <v>0.26466284463393897</v>
       </c>
     </row>
     <row r="19">
@@ -825,10 +825,10 @@
         <v>-0</v>
       </c>
       <c r="C19" s="10">
-        <v>-0.030764791677533827</v>
+        <v>-0.026880217974998732</v>
       </c>
       <c r="D19" s="10">
-        <v>0.053571250065512416</v>
+        <v>0.054108652212336177</v>
       </c>
     </row>
     <row r="20">
@@ -839,10 +839,10 @@
         <v>-0.015300141394153956</v>
       </c>
       <c r="C20" s="10">
-        <v>-0.3880158885135227</v>
+        <v>-0.38722166404384528</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01973655952222321</v>
+        <v>0.01929049605725569</v>
       </c>
     </row>
     <row r="21">
@@ -853,10 +853,10 @@
         <v>0.020003700580808088</v>
       </c>
       <c r="C21" s="10">
-        <v>0.54174082670559254</v>
+        <v>0.55063084567165321</v>
       </c>
       <c r="D21" s="10">
-        <v>-0.039361407289479365</v>
+        <v>-0.038793806279521281</v>
       </c>
     </row>
     <row r="22">
@@ -867,10 +867,10 @@
         <v>-0.0042301167062339749</v>
       </c>
       <c r="C22" s="10">
-        <v>0.1180102403937062</v>
+        <v>0.123306374112818</v>
       </c>
       <c r="D22" s="10">
-        <v>-0.27785532349524383</v>
+        <v>-0.28053797983474182</v>
       </c>
     </row>
     <row r="23">
@@ -881,10 +881,10 @@
         <v>-0.026728240766609516</v>
       </c>
       <c r="C23" s="10">
-        <v>0.027076324948148597</v>
+        <v>0.031804497477322537</v>
       </c>
       <c r="D23" s="10">
-        <v>-0.89276998644822891</v>
+        <v>-0.90207211344571669</v>
       </c>
     </row>
     <row r="24">
@@ -895,10 +895,10 @@
         <v>0.002290687025479494</v>
       </c>
       <c r="C24" s="10">
-        <v>-0.31989854388786565</v>
+        <v>-0.31868753882189194</v>
       </c>
       <c r="D24" s="10">
-        <v>0.50440571952501001</v>
+        <v>0.50917080105631174</v>
       </c>
     </row>
     <row r="25">
@@ -909,10 +909,10 @@
         <v>-0.01972873554070181</v>
       </c>
       <c r="C25" s="10">
-        <v>-0.35698072799989611</v>
+        <v>-0.35585036726869795</v>
       </c>
       <c r="D25" s="10">
-        <v>-0.16497206328453493</v>
+        <v>-0.16730391197277472</v>
       </c>
     </row>
     <row r="26">
@@ -923,10 +923,10 @@
         <v>0.033273062729940663</v>
       </c>
       <c r="C26" s="10">
-        <v>0.16120745793108485</v>
+        <v>0.16645822999315091</v>
       </c>
       <c r="D26" s="10">
-        <v>0.88818973331376716</v>
+        <v>0.89783219301959039</v>
       </c>
     </row>
     <row r="27">
@@ -937,10 +937,10 @@
         <v>0.079631146313895507</v>
       </c>
       <c r="C27" s="10">
-        <v>0.947891255479682</v>
+        <v>0.95979825329677027</v>
       </c>
       <c r="D27" s="10">
-        <v>1.3755011603070262</v>
+        <v>1.3916457382946501</v>
       </c>
     </row>
     <row r="28">
@@ -951,10 +951,10 @@
         <v>0.014093472423733218</v>
       </c>
       <c r="C28" s="10">
-        <v>0.46181873991383382</v>
+        <v>0.47004663854340822</v>
       </c>
       <c r="D28" s="10">
-        <v>-0.1279953751974727</v>
+        <v>-0.12849936483902599</v>
       </c>
     </row>
     <row r="29">
@@ -965,10 +965,10 @@
         <v>-0.013344585877866414</v>
       </c>
       <c r="C29" s="10">
-        <v>-0.42505801541699506</v>
+        <v>-0.42462584750460536</v>
       </c>
       <c r="D29" s="10">
-        <v>0.13166304422481959</v>
+        <v>0.13232763747117815</v>
       </c>
     </row>
     <row r="30">
@@ -979,10 +979,10 @@
         <v>0.0074844326131547172</v>
       </c>
       <c r="C30" s="10">
-        <v>0.062603843696284009</v>
+        <v>0.067255121832847028</v>
       </c>
       <c r="D30" s="10">
-        <v>0.17601457651027461</v>
+        <v>0.17800237154670348</v>
       </c>
     </row>
     <row r="31">
@@ -993,10 +993,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="10">
-        <v>-0.10528229877764909</v>
+        <v>-0.10207983661669513</v>
       </c>
       <c r="D31" s="10">
-        <v>0.15052286578839888</v>
+        <v>0.15194773476862961</v>
       </c>
     </row>
     <row r="32">
@@ -1007,10 +1007,10 @@
         <v>0.011782594290274341</v>
       </c>
       <c r="C32" s="10">
-        <v>0.089596404672313959</v>
+        <v>0.094444248375599574</v>
       </c>
       <c r="D32" s="10">
-        <v>0.28097489619710975</v>
+        <v>0.28411274004552411</v>
       </c>
     </row>
     <row r="33">
@@ -1021,10 +1021,10 @@
         <v>-0.012338320748559822</v>
       </c>
       <c r="C33" s="10">
-        <v>-0.23525028454005262</v>
+        <v>-0.2330924986544827</v>
       </c>
       <c r="D33" s="10">
-        <v>-0.082493187854455946</v>
+        <v>-0.083744606732164203</v>
       </c>
     </row>
     <row r="34">
@@ -1035,10 +1035,10 @@
         <v>-0.0075360080729134481</v>
       </c>
       <c r="C34" s="10">
-        <v>-0.10935140969554266</v>
+        <v>-0.10609762397995555</v>
       </c>
       <c r="D34" s="10">
-        <v>-0.089785211404953963</v>
+        <v>-0.090891906052962407</v>
       </c>
     </row>
     <row r="35">
@@ -1049,10 +1049,10 @@
         <v>0.041314915501904179</v>
       </c>
       <c r="C35" s="10">
-        <v>0.51963710264748386</v>
+        <v>0.52807431898820689</v>
       </c>
       <c r="D35" s="10">
-        <v>0.68393985115736</v>
+        <v>0.6920667957343094</v>
       </c>
     </row>
     <row r="36">
@@ -1063,10 +1063,10 @@
         <v>-0.06223607947719377</v>
       </c>
       <c r="C36" s="10">
-        <v>-1.1620046568662841</v>
+        <v>-1.1677436600069067</v>
       </c>
       <c r="D36" s="10">
-        <v>-0.5029244033616429</v>
+        <v>-0.51022161069511407</v>
       </c>
     </row>
     <row r="37">
@@ -1077,10 +1077,10 @@
         <v>0.0035922622717185684</v>
       </c>
       <c r="C37" s="10">
-        <v>0.23786781228124204</v>
+        <v>0.24416915054152744</v>
       </c>
       <c r="D37" s="10">
-        <v>-0.17886180680189512</v>
+        <v>-0.18029384126480733</v>
       </c>
     </row>
     <row r="38">
@@ -1091,10 +1091,10 @@
         <v>-0.013291381565700396</v>
       </c>
       <c r="C38" s="10">
-        <v>-0.41173142960712789</v>
+        <v>-0.41117789932476845</v>
       </c>
       <c r="D38" s="10">
-        <v>0.11605833493663145</v>
+        <v>0.11658243011231914</v>
       </c>
     </row>
     <row r="39">
@@ -1105,10 +1105,10 @@
         <v>-0.027903113895539917</v>
       </c>
       <c r="C39" s="10">
-        <v>-0.65678312536554795</v>
+        <v>-0.65830099459931779</v>
       </c>
       <c r="D39" s="10">
-        <v>-0.041318717904007263</v>
+        <v>-0.042878644530079786</v>
       </c>
     </row>
     <row r="40">
@@ -1119,10 +1119,10 @@
         <v>0.0072338875048242627</v>
       </c>
       <c r="C40" s="10">
-        <v>-0.079041976143715553</v>
+        <v>-0.075684337891880879</v>
       </c>
       <c r="D40" s="10">
-        <v>0.35213864693608599</v>
+        <v>0.35572759744735427</v>
       </c>
     </row>
     <row r="41">
@@ -1133,10 +1133,10 @@
         <v>0.026616563038507773</v>
       </c>
       <c r="C41" s="10">
-        <v>0.21873269564635001</v>
+        <v>0.22458827108067522</v>
       </c>
       <c r="D41" s="10">
-        <v>0.59640743485958381</v>
+        <v>0.60308588070140179</v>
       </c>
     </row>
     <row r="42">
@@ -1147,10 +1147,10 @@
         <v>0.0070719179118647058</v>
       </c>
       <c r="C42" s="10">
-        <v>-0.75157057380150893</v>
+        <v>-0.75436716268636639</v>
       </c>
       <c r="D42" s="10">
-        <v>1.2218588432248505</v>
+        <v>1.2334018264822957</v>
       </c>
     </row>
     <row r="43">
@@ -1161,10 +1161,10 @@
         <v>-0</v>
       </c>
       <c r="C43" s="10">
-        <v>-0.077453160555788422</v>
+        <v>-0.073995958574460632</v>
       </c>
       <c r="D43" s="10">
-        <v>0.11431553653407986</v>
+        <v>0.11540897417508156</v>
       </c>
     </row>
     <row r="44">
@@ -1175,10 +1175,10 @@
         <v>-0.0191429014733808</v>
       </c>
       <c r="C44" s="10">
-        <v>-0.29567312979928378</v>
+        <v>-0.29398846251416128</v>
       </c>
       <c r="D44" s="10">
-        <v>-0.22564419656970583</v>
+        <v>-0.22850562265897503</v>
       </c>
     </row>
     <row r="45">
@@ -1189,10 +1189,10 @@
         <v>-0.00019057254051681096</v>
       </c>
       <c r="C45" s="10">
-        <v>-0.18169177811022902</v>
+        <v>-0.17918650624641391</v>
       </c>
       <c r="D45" s="10">
-        <v>0.24372519427354469</v>
+        <v>0.24599481820584948</v>
       </c>
     </row>
     <row r="46">
@@ -1203,10 +1203,10 @@
         <v>-0.0049802745777615736</v>
       </c>
       <c r="C46" s="10">
-        <v>-0.62075234091867049</v>
+        <v>-0.62220980791766622</v>
       </c>
       <c r="D46" s="10">
-        <v>0.65886979549856839</v>
+        <v>0.66472861414552731</v>
       </c>
     </row>
     <row r="47">
@@ -1217,10 +1217,10 @@
         <v>-0.032845967973430167</v>
       </c>
       <c r="C47" s="10">
-        <v>-0.69055302445199584</v>
+        <v>-0.69232191993420855</v>
       </c>
       <c r="D47" s="10">
-        <v>-0.15847217003176683</v>
+        <v>-0.16132214734338007</v>
       </c>
     </row>
     <row r="48">
@@ -1231,10 +1231,10 @@
         <v>-0.020850974089133556</v>
       </c>
       <c r="C48" s="10">
-        <v>-0.38926912548315851</v>
+        <v>-0.38842113361654734</v>
       </c>
       <c r="D48" s="10">
-        <v>-0.15953728698838404</v>
+        <v>-0.16186880589893729</v>
       </c>
     </row>
     <row r="49">
@@ -1245,10 +1245,10 @@
         <v>-0.0075793529644209434</v>
       </c>
       <c r="C49" s="10">
-        <v>0.095354864305904119</v>
+        <v>0.10048298102554801</v>
       </c>
       <c r="D49" s="10">
-        <v>-0.35753262489896892</v>
+        <v>-0.36109211005752129</v>
       </c>
     </row>
     <row r="50">
@@ -1259,10 +1259,10 @@
         <v>0.044294962071666805</v>
       </c>
       <c r="C50" s="10">
-        <v>0.92002475661832672</v>
+        <v>0.93209198024019224</v>
       </c>
       <c r="D50" s="10">
-        <v>0.26013339013905967</v>
+        <v>0.2645121623830215</v>
       </c>
     </row>
     <row r="51">
@@ -1273,10 +1273,10 @@
         <v>-0.063838203845931252</v>
       </c>
       <c r="C51" s="10">
-        <v>-1.186075311988315</v>
+        <v>-1.1920158210574383</v>
       </c>
       <c r="D51" s="10">
-        <v>-0.52382110442393681</v>
+        <v>-0.53138014476583184</v>
       </c>
     </row>
     <row r="52">
@@ -1287,10 +1287,10 @@
         <v>0.0094247772599463341</v>
       </c>
       <c r="C52" s="10">
-        <v>-0.17257190604756442</v>
+        <v>-0.17009616313099618</v>
       </c>
       <c r="D52" s="10">
-        <v>0.5452287116460659</v>
+        <v>0.55068162973684975</v>
       </c>
     </row>
     <row r="53">
@@ -1301,10 +1301,10 @@
         <v>0.0018070107845080449</v>
       </c>
       <c r="C53" s="10">
-        <v>-0.3233837014553767</v>
+        <v>-0.32219891383944066</v>
       </c>
       <c r="D53" s="10">
-        <v>0.49317686472446992</v>
+        <v>0.4978178615609426</v>
       </c>
     </row>
     <row r="54">
@@ -1315,10 +1315,10 @@
         <v>0.027387592271801337</v>
       </c>
       <c r="C54" s="10">
-        <v>0.17784783512721822</v>
+        <v>0.1833201005263978</v>
       </c>
       <c r="D54" s="10">
-        <v>0.67472924278768742</v>
+        <v>0.68215857645817735</v>
       </c>
     </row>
     <row r="55">
@@ -1329,10 +1329,10 @@
         <v>0.024000332421887319</v>
       </c>
       <c r="C55" s="10">
-        <v>0.32985452228833628</v>
+        <v>0.33675802320192344</v>
       </c>
       <c r="D55" s="10">
-        <v>0.36656721927497876</v>
+        <v>0.37102656717680488</v>
       </c>
     </row>
     <row r="56">
@@ -1343,10 +1343,10 @@
         <v>0.017838267596501183</v>
       </c>
       <c r="C56" s="10">
-        <v>0.07812301910784171</v>
+        <v>0.082794666208460169</v>
       </c>
       <c r="D56" s="10">
-        <v>0.49325982468253043</v>
+        <v>0.49860752881864578</v>
       </c>
     </row>
     <row r="57">
@@ -1357,10 +1357,10 @@
         <v>-0.0011586402916066519</v>
       </c>
       <c r="C57" s="10">
-        <v>-0.13769061817756914</v>
+        <v>-0.13477119478030433</v>
       </c>
       <c r="D57" s="10">
-        <v>0.15492731668089205</v>
+        <v>0.15634148116344981</v>
       </c>
     </row>
     <row r="58">
@@ -1371,10 +1371,10 @@
         <v>0.0021649711934588127</v>
       </c>
       <c r="C58" s="10">
-        <v>0.71244520199666894</v>
+        <v>0.72310745837522161</v>
       </c>
       <c r="D58" s="10">
-        <v>-0.842830746003565</v>
+        <v>-0.8504034104074355</v>
       </c>
     </row>
     <row r="59">
@@ -1385,10 +1385,10 @@
         <v>0.035166391496261738</v>
       </c>
       <c r="C59" s="10">
-        <v>-0.44385545151854289</v>
+        <v>-0.44416550135182731</v>
       </c>
       <c r="D59" s="10">
-        <v>1.7371163301381543</v>
+        <v>1.7546129905805263</v>
       </c>
     </row>
     <row r="60">
@@ -1399,10 +1399,10 @@
         <v>-0.052728340372419601</v>
       </c>
       <c r="C60" s="10">
-        <v>-1.2777498819354258</v>
+        <v>-1.2846601279771361</v>
       </c>
       <c r="D60" s="10">
-        <v>-0.042471209763185837</v>
+        <v>-0.045134882642775903</v>
       </c>
     </row>
     <row r="61">
@@ -1413,10 +1413,10 @@
         <v>0.029583091018795443</v>
       </c>
       <c r="C61" s="10">
-        <v>0.54784249837203347</v>
+        <v>0.55667578329593914</v>
       </c>
       <c r="D61" s="10">
-        <v>0.26489703114710117</v>
+        <v>0.26867156056367164</v>
       </c>
     </row>
     <row r="62">
@@ -1427,10 +1427,10 @@
         <v>-0.0054667913938969571</v>
       </c>
       <c r="C62" s="10">
-        <v>-0.18496392077649404</v>
+        <v>-0.18242658953774668</v>
       </c>
       <c r="D62" s="10">
-        <v>0.076027862443945646</v>
+        <v>0.076530091789794613</v>
       </c>
     </row>
     <row r="63">
@@ -1441,10 +1441,10 @@
         <v>0.0061864297946760847</v>
       </c>
       <c r="C63" s="10">
-        <v>0.11599925513832836</v>
+        <v>0.12115455478896116</v>
       </c>
       <c r="D63" s="10">
-        <v>0.064241483796012772</v>
+        <v>0.06514898203201365</v>
       </c>
     </row>
     <row r="64">
@@ -1455,10 +1455,10 @@
         <v>-0.02464058399279876</v>
       </c>
       <c r="C64" s="10">
-        <v>0.25625632623921113</v>
+        <v>0.26305780938966616</v>
       </c>
       <c r="D64" s="10">
-        <v>-1.122908746770338</v>
+        <v>-1.13422556543947</v>
       </c>
     </row>
     <row r="65">
@@ -1469,10 +1469,10 @@
         <v>-0.0078997979979023962</v>
       </c>
       <c r="C65" s="10">
-        <v>-0.18590526997841705</v>
+        <v>-0.18334796035012813</v>
       </c>
       <c r="D65" s="10">
-        <v>-0.0020402750614247948</v>
+        <v>-0.0023597978863863956</v>
       </c>
     </row>
     <row r="66">
@@ -1483,10 +1483,10 @@
         <v>-0.0022130858495569192</v>
       </c>
       <c r="C66" s="10">
-        <v>-0.14540632076350041</v>
+        <v>-0.14254513171731867</v>
       </c>
       <c r="D66" s="10">
-        <v>0.13060099316671275</v>
+        <v>0.13174604830630909</v>
       </c>
     </row>
     <row r="67">
@@ -1497,10 +1497,10 @@
         <v>-0.007508420092460371</v>
       </c>
       <c r="C67" s="10">
-        <v>-0.15495703927838933</v>
+        <v>-0.15212103844672653</v>
       </c>
       <c r="D67" s="10">
-        <v>-0.029550525888072089</v>
+        <v>-0.030104634923954522</v>
       </c>
     </row>
     <row r="68">
@@ -1511,10 +1511,10 @@
         <v>-0.030086894266433725</v>
       </c>
       <c r="C68" s="10">
-        <v>-0.56956107912767306</v>
+        <v>-0.57025487711168044</v>
       </c>
       <c r="D68" s="10">
-        <v>-0.22597016032528233</v>
+        <v>-0.22931649677506771</v>
       </c>
     </row>
     <row r="69">
@@ -1525,10 +1525,10 @@
         <v>-0.020855706000230213</v>
       </c>
       <c r="C69" s="10">
-        <v>-0.26979827556876079</v>
+        <v>-0.26785662674792682</v>
       </c>
       <c r="D69" s="10">
-        <v>-0.31513003456514921</v>
+        <v>-0.31888601251202087</v>
       </c>
     </row>
     <row r="70">
@@ -1539,10 +1539,10 @@
         <v>-0.023365122371507528</v>
       </c>
       <c r="C70" s="10">
-        <v>-0.077465583324847154</v>
+        <v>-0.073733883822428348</v>
       </c>
       <c r="D70" s="10">
-        <v>-0.64714918597868487</v>
+        <v>-0.65405487442166921</v>
       </c>
     </row>
     <row r="71">
@@ -1553,10 +1553,10 @@
         <v>0.067018708291951362</v>
       </c>
       <c r="C71" s="10">
-        <v>1.0275032564154321</v>
+        <v>1.0402872337839659</v>
       </c>
       <c r="D71" s="10">
-        <v>0.86087572319215211</v>
+        <v>0.87175417215064743</v>
       </c>
     </row>
     <row r="72">
@@ -1567,10 +1567,10 @@
         <v>-0.020619271474677459</v>
       </c>
       <c r="C72" s="10">
-        <v>-0.22648252983908512</v>
+        <v>-0.22414716013099686</v>
       </c>
       <c r="D72" s="10">
-        <v>-0.36378082390220989</v>
+        <v>-0.3679717254310591</v>
       </c>
     </row>
     <row r="73">
@@ -1581,10 +1581,10 @@
         <v>-0.064254270491591089</v>
       </c>
       <c r="C73" s="10">
-        <v>-1.3196274321359918</v>
+        <v>-1.3267855483404256</v>
       </c>
       <c r="D73" s="10">
-        <v>-0.36362183727884928</v>
+        <v>-0.36973278201357579</v>
       </c>
     </row>
     <row r="74">
@@ -1595,10 +1595,10 @@
         <v>0.035225904205325051</v>
       </c>
       <c r="C74" s="10">
-        <v>0.45784096637324884</v>
+        <v>0.46578408329117016</v>
       </c>
       <c r="D74" s="10">
-        <v>0.56589633532098094</v>
+        <v>0.57267460997224673</v>
       </c>
     </row>
     <row r="75">
@@ -1609,10 +1609,10 @@
         <v>-0.0024406567188806549</v>
       </c>
       <c r="C75" s="10">
-        <v>-0.17290726551987723</v>
+        <v>-0.17029513745703748</v>
       </c>
       <c r="D75" s="10">
-        <v>0.15896467651444676</v>
+        <v>0.16035934329801765</v>
       </c>
     </row>
     <row r="76">
@@ -1623,10 +1623,10 @@
         <v>-0.020577726027900735</v>
       </c>
       <c r="C76" s="10">
-        <v>0.022030165188922222</v>
+        <v>0.026639859391989221</v>
       </c>
       <c r="D76" s="10">
-        <v>-0.68575632382249141</v>
+        <v>-0.69289266575302666</v>
       </c>
     </row>
     <row r="77">
@@ -1637,10 +1637,10 @@
         <v>0.18976921448872325</v>
       </c>
       <c r="C77" s="10">
-        <v>2.7711305146811971</v>
+        <v>2.798432456082907</v>
       </c>
       <c r="D77" s="10">
-        <v>2.592814793647042</v>
+        <v>2.6249523147836471</v>
       </c>
     </row>
     <row r="78">
@@ -1651,10 +1651,10 @@
         <v>-0.2580856239069555</v>
       </c>
       <c r="C78" s="10">
-        <v>-4.8367647898871722</v>
+        <v>-4.8738396485848261</v>
       </c>
       <c r="D78" s="10">
-        <v>-2.1046809402248665</v>
+        <v>-2.1352645354190312</v>
       </c>
     </row>
     <row r="79">
@@ -1665,10 +1665,10 @@
         <v>-0.13199721617207724</v>
       </c>
       <c r="C79" s="10">
-        <v>-1.1997013673063728</v>
+        <v>-1.2049655296647621</v>
       </c>
       <c r="D79" s="10">
-        <v>-2.7274287093064706</v>
+        <v>-2.7581603624774096</v>
       </c>
     </row>
     <row r="80">
@@ -1679,10 +1679,10 @@
         <v>-0.025784070302994511</v>
       </c>
       <c r="C80" s="10">
-        <v>-0.024245973030643367</v>
+        <v>-0.019998686733025878</v>
       </c>
       <c r="D80" s="10">
-        <v>-0.7952257063732493</v>
+        <v>-0.80359336423605809</v>
       </c>
     </row>
     <row r="81">
@@ -1693,10 +1693,10 @@
         <v>-0.079675263411411124</v>
       </c>
       <c r="C81" s="10">
-        <v>-0.64264803781701052</v>
+        <v>-0.6434280383958072</v>
       </c>
       <c r="D81" s="10">
-        <v>-1.7469892286603901</v>
+        <v>-1.7664421898076343</v>
       </c>
     </row>
     <row r="82">
@@ -1707,10 +1707,10 @@
         <v>0.1581201943874101</v>
       </c>
       <c r="C82" s="10">
-        <v>4.0394738780534922</v>
+        <v>4.0787578371631072</v>
       </c>
       <c r="D82" s="10">
-        <v>-0.088830981081805205</v>
+        <v>-0.082634151123582786</v>
       </c>
     </row>
     <row r="83">
@@ -1721,10 +1721,10 @@
         <v>0.02867599300769642</v>
       </c>
       <c r="C83" s="10">
-        <v>-0.75936205138014046</v>
+        <v>-0.76248387475499091</v>
       </c>
       <c r="D83" s="10">
-        <v>1.936083493459932</v>
+        <v>1.9551156319663552</v>
       </c>
     </row>
     <row r="84">
@@ -1735,10 +1735,10 @@
         <v>-0.016102019794642132</v>
       </c>
       <c r="C84" s="10">
-        <v>0.96996360604877618</v>
+        <v>0.98319780353286523</v>
       </c>
       <c r="D84" s="10">
-        <v>-1.7732074483377114</v>
+        <v>-1.7901009099815437</v>
       </c>
     </row>
     <row r="85">
@@ -1749,10 +1749,10 @@
         <v>-0.072266471826937573</v>
       </c>
       <c r="C85" s="10">
-        <v>0.18972386959764809</v>
+        <v>0.19647608303189526</v>
       </c>
       <c r="D85" s="10">
-        <v>-2.5884973681341834</v>
+        <v>-2.6153269980705161</v>
       </c>
     </row>
     <row r="86">
@@ -1763,10 +1763,10 @@
         <v>0.016294756565038447</v>
       </c>
       <c r="C86" s="10">
-        <v>0.23047194810276816</v>
+        <v>0.23655629384478616</v>
       </c>
       <c r="D86" s="10">
-        <v>0.2447412098001448</v>
+        <v>0.24774607735041415</v>
       </c>
     </row>
     <row r="87">
@@ -1777,10 +1777,10 @@
         <v>0.095314706273988567</v>
       </c>
       <c r="C87" s="10">
-        <v>1.4099237215096287</v>
+        <v>1.425875700340212</v>
       </c>
       <c r="D87" s="10">
-        <v>1.2855049888987131</v>
+        <v>1.3015164049907491</v>
       </c>
     </row>
     <row r="88">
@@ -1791,10 +1791,10 @@
         <v>-0.0095965437305960202</v>
       </c>
       <c r="C88" s="10">
-        <v>0.2083672859520648</v>
+        <v>0.21455359356684112</v>
       </c>
       <c r="D88" s="10">
-        <v>-0.57030960989428503</v>
+        <v>-0.57590562200307693</v>
       </c>
     </row>
     <row r="89">
@@ -1805,10 +1805,10 @@
         <v>0.079140272690187335</v>
       </c>
       <c r="C89" s="10">
-        <v>0.95220465415966848</v>
+        <v>0.96415690482882221</v>
       </c>
       <c r="D89" s="10">
-        <v>1.3538913634758516</v>
+        <v>1.3698165157089446</v>
       </c>
     </row>
     <row r="90">
@@ -1819,10 +1819,10 @@
         <v>-0.024551079135803448</v>
       </c>
       <c r="C90" s="10">
-        <v>0.81679193031403907</v>
+        <v>0.82872334105971046</v>
       </c>
       <c r="D90" s="10">
-        <v>-1.8492811988668856</v>
+        <v>-1.8672430778478055</v>
       </c>
     </row>
     <row r="91">
@@ -1833,10 +1833,10 @@
         <v>0.033796992932977728</v>
       </c>
       <c r="C91" s="10">
-        <v>0.5933505181016645</v>
+        <v>0.60255084401374959</v>
       </c>
       <c r="D91" s="10">
-        <v>0.34302159356651724</v>
+        <v>0.34769681465525004</v>
       </c>
     </row>
     <row r="92">
@@ -1847,10 +1847,10 @@
         <v>-0.05535474293448945</v>
       </c>
       <c r="C92" s="10">
-        <v>-0.34544744455648863</v>
+        <v>-0.34379279759320103</v>
       </c>
       <c r="D92" s="10">
-        <v>-1.3410467241325623</v>
+        <v>-1.3557128343191414</v>
       </c>
     </row>
     <row r="93">
@@ -1861,10 +1861,10 @@
         <v>-0.02238373963120421</v>
       </c>
       <c r="C93" s="10">
-        <v>-0.21425708412717612</v>
+        <v>-0.21178906838603803</v>
       </c>
       <c r="D93" s="10">
-        <v>-0.43719172986443083</v>
+        <v>-0.44213231305319184</v>
       </c>
     </row>
     <row r="94">
@@ -1875,10 +1875,10 @@
         <v>0.0070150981699402051</v>
       </c>
       <c r="C94" s="10">
-        <v>-0.85017975369351073</v>
+        <v>-0.85387831446633333</v>
       </c>
       <c r="D94" s="10">
-        <v>1.3483033445835675</v>
+        <v>1.3610012618555682</v>
       </c>
     </row>
     <row r="95">
@@ -1889,10 +1889,10 @@
         <v>-0.0073502047599428733</v>
       </c>
       <c r="C95" s="10">
-        <v>-0.31319065513961852</v>
+        <v>-0.3118049382210063</v>
       </c>
       <c r="D95" s="10">
-        <v>0.18147693781002522</v>
+        <v>0.18286147979787884</v>
       </c>
     </row>
     <row r="96">
@@ -1903,10 +1903,10 @@
         <v>-0.028822338075210948</v>
       </c>
       <c r="C96" s="10">
-        <v>-0.36084016128413476</v>
+        <v>-0.35963825119916815</v>
       </c>
       <c r="D96" s="10">
-        <v>-0.45631571656342917</v>
+        <v>-0.46171488345975875</v>
       </c>
     </row>
     <row r="97">
@@ -1917,10 +1917,10 @@
         <v>-0.0018589616987090087</v>
       </c>
       <c r="C97" s="10">
-        <v>0.39170406464533053</v>
+        <v>0.39947764358108467</v>
       </c>
       <c r="D97" s="10">
-        <v>-0.55666981188499598</v>
+        <v>-0.56180023927579359</v>
       </c>
     </row>
     <row r="98">
@@ -1931,10 +1931,10 @@
         <v>-0.006509749082865929</v>
       </c>
       <c r="C98" s="10">
-        <v>-0.44024293211143151</v>
+        <v>-0.44003009261617182</v>
       </c>
       <c r="D98" s="10">
-        <v>0.37417021399036343</v>
+        <v>0.37735562413658502</v>
       </c>
     </row>
     <row r="99">
@@ -1945,10 +1945,10 @@
         <v>0.0057035792674715157</v>
       </c>
       <c r="C99" s="10">
-        <v>-0.13647539070679698</v>
+        <v>-0.13362549541760105</v>
       </c>
       <c r="D99" s="10">
-        <v>0.37698936175825876</v>
+        <v>0.38073840024777833</v>
       </c>
     </row>
     <row r="100">
@@ -1959,10 +1959,10 @@
         <v>-0.00012738232006064779</v>
       </c>
       <c r="C100" s="10">
-        <v>0.44029510629128843</v>
+        <v>0.44849312213721487</v>
       </c>
       <c r="D100" s="10">
-        <v>-0.56345655870652389</v>
+        <v>-0.56857285865803509</v>
       </c>
     </row>
     <row r="101">
@@ -1973,10 +1973,10 @@
         <v>0.027972005567163137</v>
       </c>
       <c r="C101" s="10">
-        <v>-0.36847788455055208</v>
+        <v>-0.36801339419385426</v>
       </c>
       <c r="D101" s="10">
-        <v>1.4045771335136374</v>
+        <v>1.4187130171180882</v>
       </c>
     </row>
     <row r="102">
@@ -1987,10 +1987,10 @@
         <v>0.035577084651876013</v>
       </c>
       <c r="C102" s="10">
-        <v>-0.35606968634297137</v>
+        <v>-0.35558099776073282</v>
       </c>
       <c r="D102" s="10">
-        <v>1.6362866309867599</v>
+        <v>1.6528784109183958</v>
       </c>
     </row>
     <row r="103">
@@ -2001,10 +2001,10 @@
         <v>-0.014179920856832978</v>
       </c>
       <c r="C103" s="10">
-        <v>-0.050923390333885231</v>
+        <v>-0.047056685380404022</v>
       </c>
       <c r="D103" s="10">
-        <v>-0.3823318678116448</v>
+        <v>-0.38640901876006767</v>
       </c>
     </row>
     <row r="104">
@@ -2015,10 +2015,10 @@
         <v>-0.0076456162124952758</v>
       </c>
       <c r="C104" s="10">
-        <v>-0.10658280862467366</v>
+        <v>-0.10330239171287152</v>
       </c>
       <c r="D104" s="10">
-        <v>-0.096959506045436905</v>
+        <v>-0.098136698768762534</v>
       </c>
     </row>
     <row r="105">
@@ -2029,10 +2029,10 @@
         <v>-0.0089396552101357538</v>
       </c>
       <c r="C105" s="10">
-        <v>-0.1766375881536888</v>
+        <v>-0.17398322338288205</v>
       </c>
       <c r="D105" s="10">
-        <v>-0.047987529201320135</v>
+        <v>-0.048773430658405954</v>
       </c>
     </row>
     <row r="106">
@@ -2043,10 +2043,10 @@
         <v>-0.0094429074814099869</v>
       </c>
       <c r="C106" s="10">
-        <v>-0.22171129630190872</v>
+        <v>-0.21946360837413087</v>
       </c>
       <c r="D106" s="10">
-        <v>-0.0057452505914157952</v>
+        <v>-0.0061666396170134679</v>
       </c>
     </row>
     <row r="107">
@@ -2057,10 +2057,10 @@
         <v>0.0016462451062200806</v>
       </c>
       <c r="C107" s="10">
-        <v>-0.18740717144403191</v>
+        <v>-0.18497580481768433</v>
       </c>
       <c r="D107" s="10">
-        <v>0.31102404866770872</v>
+        <v>0.31399059228301951</v>
       </c>
     </row>
     <row r="108">
@@ -2071,10 +2071,10 @@
         <v>0.088332230201475528</v>
       </c>
       <c r="C108" s="10">
-        <v>1.0227166731475654</v>
+        <v>1.0352063368362792</v>
       </c>
       <c r="D108" s="10">
-        <v>1.5617215590260036</v>
+        <v>1.5799539027475027</v>
       </c>
     </row>
     <row r="109">
@@ -2085,10 +2085,10 @@
         <v>-0.058364560089301985</v>
       </c>
       <c r="C109" s="10">
-        <v>-1.027622004610522</v>
+        <v>-1.0321764102438877</v>
       </c>
       <c r="D109" s="10">
-        <v>-0.55158932856637477</v>
+        <v>-0.55916151530457814</v>
       </c>
     </row>
     <row r="110">
@@ -2099,10 +2099,10 @@
         <v>0.1501525191984707</v>
       </c>
       <c r="C110" s="10">
-        <v>1.7685188741889437</v>
+        <v>1.7871088174829559</v>
       </c>
       <c r="D110" s="10">
-        <v>2.6061432394353536</v>
+        <v>2.6366582156477882</v>
       </c>
     </row>
     <row r="111">
@@ -2113,10 +2113,10 @@
         <v>-0.02917338802567979</v>
       </c>
       <c r="C111" s="10">
-        <v>-0.83976766276634973</v>
+        <v>-0.84294558954031829</v>
       </c>
       <c r="D111" s="10">
-        <v>0.15535595835186117</v>
+        <v>0.15554039695693506</v>
       </c>
     </row>
     <row r="112">
@@ -2127,10 +2127,10 @@
         <v>-0.12621454957433992</v>
       </c>
       <c r="C112" s="10">
-        <v>-1.9867135428841893</v>
+        <v>-1.9992497492363008</v>
       </c>
       <c r="D112" s="10">
-        <v>-1.5150200806978293</v>
+        <v>-1.5343990547665274</v>
       </c>
     </row>
     <row r="113">
@@ -2141,10 +2141,10 @@
         <v>-0.048410372071149038</v>
       </c>
       <c r="C113" s="10">
-        <v>-1.0190283505464257</v>
+        <v>-1.0236210843526112</v>
       </c>
       <c r="D113" s="10">
-        <v>-0.2383582659670237</v>
+        <v>-0.24262488703148882</v>
       </c>
     </row>
     <row r="114">
@@ -2155,10 +2155,10 @@
         <v>0.02508867141588772</v>
       </c>
       <c r="C114" s="10">
-        <v>0.083086167073928033</v>
+        <v>0.087718031092913679</v>
       </c>
       <c r="D114" s="10">
-        <v>0.72309672384880674</v>
+        <v>0.73086756471292358</v>
       </c>
     </row>
     <row r="115">
@@ -2169,10 +2169,10 @@
         <v>-0.14322937895949248</v>
       </c>
       <c r="C115" s="10">
-        <v>-0.52903621008746815</v>
+        <v>-0.52802928699759177</v>
       </c>
       <c r="D115" s="10">
-        <v>-3.9660648663992619</v>
+        <v>-4.0086292503029526</v>
       </c>
     </row>
     <row r="116">
@@ -2183,10 +2183,10 @@
         <v>-0.047270537797475143</v>
       </c>
       <c r="C116" s="10">
-        <v>-0.28445356749471512</v>
+        <v>-0.28233561435015764</v>
       </c>
       <c r="D116" s="10">
-        <v>-1.1569350690515465</v>
+        <v>-1.1695598810277728</v>
       </c>
     </row>
     <row r="117">
@@ -2197,10 +2197,10 @@
         <v>0.088038215049007496</v>
       </c>
       <c r="C117" s="10">
-        <v>2.5511656047693507</v>
+        <v>2.5776497000778953</v>
       </c>
       <c r="D117" s="10">
-        <v>-0.43646159825571357</v>
+        <v>-0.43653298794624323</v>
       </c>
     </row>
     <row r="118">
@@ -2211,10 +2211,10 @@
         <v>-0.027307263545217259</v>
       </c>
       <c r="C118" s="10">
-        <v>-0.52124666804902497</v>
+        <v>-0.52153087910859164</v>
       </c>
       <c r="D118" s="10">
-        <v>-0.19824048346417045</v>
+        <v>-0.20121058749857682</v>
       </c>
     </row>
     <row r="119">
@@ -2225,10 +2225,10 @@
         <v>0.013143761947012961</v>
       </c>
       <c r="C119" s="10">
-        <v>1.3848479949803061</v>
+        <v>1.4015361963762805</v>
       </c>
       <c r="D119" s="10">
-        <v>-1.3598617157299928</v>
+        <v>-1.3716836720035934</v>
       </c>
     </row>
     <row r="120">
@@ -2239,10 +2239,10 @@
         <v>0.013550426916144184</v>
       </c>
       <c r="C120" s="10">
-        <v>0.42703210601259362</v>
+        <v>0.43494796037011701</v>
       </c>
       <c r="D120" s="10">
-        <v>-0.10043406041345378</v>
+        <v>-0.10070967521130093</v>
       </c>
     </row>
     <row r="121">
@@ -2253,10 +2253,10 @@
         <v>-0.0070003504169984972</v>
       </c>
       <c r="C121" s="10">
-        <v>-0.10799654161241012</v>
+        <v>-0.10473664943553268</v>
       </c>
       <c r="D121" s="10">
-        <v>-0.074090625940798086</v>
+        <v>-0.075030068858093796</v>
       </c>
     </row>
     <row r="122">
@@ -2267,10 +2267,10 @@
         <v>0.00042684033605907071</v>
       </c>
       <c r="C122" s="10">
-        <v>-0.046451802898609146</v>
+        <v>-0.042715840196618123</v>
       </c>
       <c r="D122" s="10">
-        <v>0.087891902582252587</v>
+        <v>0.088762262200110492</v>
       </c>
     </row>
     <row r="123">
@@ -2281,10 +2281,10 @@
         <v>-8.436942350717111e-07</v>
       </c>
       <c r="C123" s="10">
-        <v>0.01236153060389374</v>
+        <v>0.016640880007233669</v>
       </c>
       <c r="D123" s="10">
-        <v>-0.0025661027827580149</v>
+        <v>-0.0025426027551421061</v>
       </c>
     </row>
     <row r="124">
@@ -2295,10 +2295,10 @@
         <v>0.013539391537946588</v>
       </c>
       <c r="C124" s="10">
-        <v>0.75896139042585098</v>
+        <v>0.76991575841007953</v>
       </c>
       <c r="D124" s="10">
-        <v>-0.53265303535462905</v>
+        <v>-0.53688554262801458</v>
       </c>
     </row>
     <row r="125">
@@ -2309,10 +2309,10 @@
         <v>0.033132835541829858</v>
       </c>
       <c r="C125" s="10">
-        <v>0.30583523363436543</v>
+        <v>0.31241153429875612</v>
       </c>
       <c r="D125" s="10">
-        <v>0.69545050241446615</v>
+        <v>0.70332250837027699</v>
       </c>
     </row>
     <row r="126">
@@ -2323,10 +2323,10 @@
         <v>-0.053732234818308092</v>
       </c>
       <c r="C126" s="10">
-        <v>0.76989350937482703</v>
+        <v>0.78173859295598536</v>
       </c>
       <c r="D126" s="10">
-        <v>-2.7392919076156752</v>
+        <v>-2.7666856983776524</v>
       </c>
     </row>
     <row r="127">
@@ -2337,10 +2337,10 @@
         <v>0.0085505064519660594</v>
       </c>
       <c r="C127" s="10">
-        <v>2.8803270058376951</v>
+        <v>2.9107583709549982</v>
       </c>
       <c r="D127" s="10">
-        <v>-3.4552634538061593</v>
+        <v>-3.4864683741821216</v>
       </c>
     </row>
     <row r="128">
@@ -2351,10 +2351,10 @@
         <v>-0.001347085595402444</v>
       </c>
       <c r="C128" s="10">
-        <v>-1.0275401662735482</v>
+        <v>-1.0327639514841533</v>
       </c>
       <c r="D128" s="10">
-        <v>1.3065318670957964</v>
+        <v>1.3184791856689821</v>
       </c>
     </row>
     <row r="129">
@@ -2365,10 +2365,10 @@
         <v>-0.00062427119252311673</v>
       </c>
       <c r="C129" s="10">
-        <v>0.011423250462524705</v>
+        <v>0.015701338291711602</v>
       </c>
       <c r="D129" s="10">
-        <v>-0.021663155955395474</v>
+        <v>-0.021841917864284143</v>
       </c>
     </row>
     <row r="130">
@@ -2379,10 +2379,10 @@
         <v>0.006954394050321608</v>
       </c>
       <c r="C130" s="10">
-        <v>0.1985674168274271</v>
+        <v>0.20446949545015874</v>
       </c>
       <c r="D130" s="10">
-        <v>-0.018156167694899292</v>
+        <v>-0.01796909568793735</v>
       </c>
     </row>
     <row r="131">
@@ -2393,10 +2393,10 @@
         <v>-0.022679254356716395</v>
       </c>
       <c r="C131" s="10">
-        <v>-0.48962335364971732</v>
+        <v>-0.48967248728661994</v>
       </c>
       <c r="D131" s="10">
-        <v>-0.088555150210943345</v>
+        <v>-0.09031742896422007</v>
       </c>
     </row>
     <row r="132">
@@ -2407,10 +2407,10 @@
         <v>0.030218353248753965</v>
       </c>
       <c r="C132" s="10">
-        <v>0.16480349142003733</v>
+        <v>0.17012308264961315</v>
       </c>
       <c r="D132" s="10">
-        <v>0.7839565927097536</v>
+        <v>0.79251041629954933</v>
       </c>
     </row>
     <row r="133">
@@ -2421,10 +2421,10 @@
         <v>-0.047367524302032352</v>
       </c>
       <c r="C133" s="10">
-        <v>-0.66488285959689652</v>
+        <v>-0.66624610542832485</v>
       </c>
       <c r="D133" s="10">
-        <v>-0.66513524660548307</v>
+        <v>-0.67326253721437301</v>
       </c>
     </row>
     <row r="134">
@@ -2435,10 +2435,10 @@
         <v>0.03868644562416379</v>
       </c>
       <c r="C134" s="10">
-        <v>0.47103539978706199</v>
+        <v>0.47905862281855227</v>
       </c>
       <c r="D134" s="10">
-        <v>0.66151036422608611</v>
+        <v>0.66931624925782918</v>
       </c>
     </row>
     <row r="135">
@@ -2449,10 +2449,10 @@
         <v>-0.0036675326339608069</v>
       </c>
       <c r="C135" s="10">
-        <v>0.49257610640621269</v>
+        <v>0.50129429482061416</v>
       </c>
       <c r="D135" s="10">
-        <v>-0.74685243235189447</v>
+        <v>-0.75380337774115391</v>
       </c>
     </row>
     <row r="136">
@@ -2463,10 +2463,10 @@
         <v>-0.029121021264753941</v>
       </c>
       <c r="C136" s="10">
-        <v>-0.37109553711105769</v>
+        <v>-0.36998399131174226</v>
       </c>
       <c r="D136" s="10">
-        <v>-0.45270710822337079</v>
+        <v>-0.45808639569948262</v>
       </c>
     </row>
     <row r="137">
@@ -2477,10 +2477,10 @@
         <v>0.079056291912105975</v>
       </c>
       <c r="C137" s="10">
-        <v>1.5643330032915459</v>
+        <v>1.5818894854910046</v>
       </c>
       <c r="D137" s="10">
-        <v>0.55473976334671093</v>
+        <v>0.56334601659413874</v>
       </c>
     </row>
     <row r="138">
@@ -2491,10 +2491,10 @@
         <v>-0.046527574775247341</v>
       </c>
       <c r="C138" s="10">
-        <v>-1.7452099719971805</v>
+        <v>-1.756472089311061</v>
       </c>
       <c r="D138" s="10">
-        <v>0.76780760181338603</v>
+        <v>0.77283404018294832</v>
       </c>
     </row>
     <row r="139">
@@ -2505,10 +2505,10 @@
         <v>0.051510412032470893</v>
       </c>
       <c r="C139" s="10">
-        <v>0.47216590665196145</v>
+        <v>0.48004875741395359</v>
       </c>
       <c r="D139" s="10">
-        <v>1.0779789118890433</v>
+        <v>1.0901617411964999</v>
       </c>
     </row>
     <row r="140">
@@ -2519,10 +2519,10 @@
         <v>0.0014351694969134124</v>
       </c>
       <c r="C140" s="10">
-        <v>0.048378281048293059</v>
+        <v>0.05297043976641938</v>
       </c>
       <c r="D140" s="10">
-        <v>-0.002625612699612563</v>
+        <v>-0.0025394215361245992</v>
       </c>
     </row>
     <row r="141">
@@ -2533,10 +2533,10 @@
         <v>0.011635633885722856</v>
       </c>
       <c r="C141" s="10">
-        <v>0.26025269258812062</v>
+        <v>0.26666440144418191</v>
       </c>
       <c r="D141" s="10">
-        <v>0.054151616476613366</v>
+        <v>0.05520671462401084</v>
       </c>
     </row>
     <row r="142">
@@ -2547,10 +2547,10 @@
         <v>-0.049593975063609762</v>
       </c>
       <c r="C142" s="10">
-        <v>-1.0163394410898789</v>
+        <v>-1.0208936504683832</v>
       </c>
       <c r="D142" s="10">
-        <v>-0.28043090020646272</v>
+        <v>-0.28513476271043581</v>
       </c>
     </row>
     <row r="143">
@@ -2561,10 +2561,10 @@
         <v>0.025900140325720869</v>
       </c>
       <c r="C143" s="10">
-        <v>0.90739232508119749</v>
+        <v>0.91956011019622008</v>
       </c>
       <c r="D143" s="10">
-        <v>-0.3229274123951249</v>
+        <v>-0.32469583799014534</v>
       </c>
     </row>
     <row r="144">
@@ -2575,10 +2575,10 @@
         <v>-0.009850974999955988</v>
       </c>
       <c r="C144" s="10">
-        <v>-0.18596646101963632</v>
+        <v>-0.18338677925347729</v>
       </c>
       <c r="D144" s="10">
-        <v>-0.065550484733052194</v>
+        <v>-0.066537282987796195</v>
       </c>
     </row>
     <row r="145">
@@ -2589,10 +2589,10 @@
         <v>0.029942500232681347</v>
       </c>
       <c r="C145" s="10">
-        <v>0.46288137566934967</v>
+        <v>0.47093272708714129</v>
       </c>
       <c r="D145" s="10">
-        <v>0.3871497227795484</v>
+        <v>0.39205914454718999</v>
       </c>
     </row>
     <row r="146">
@@ -2603,10 +2603,10 @@
         <v>0.026831911802320967</v>
       </c>
       <c r="C146" s="10">
-        <v>0.70308843152211753</v>
+        <v>0.71337512719251406</v>
       </c>
       <c r="D146" s="10">
-        <v>-0.026749257812886604</v>
+        <v>-0.025765523676892266</v>
       </c>
     </row>
     <row r="147">
@@ -2617,10 +2617,10 @@
         <v>0.012943045819617426</v>
       </c>
       <c r="C147" s="10">
-        <v>-0.89001168488221882</v>
+        <v>-0.89414452695429891</v>
       </c>
       <c r="D147" s="10">
-        <v>1.5933217499103209</v>
+        <v>1.6085235356857044</v>
       </c>
     </row>
     <row r="148">
@@ -2631,10 +2631,10 @@
         <v>-0.031892469499643326</v>
       </c>
       <c r="C148" s="10">
-        <v>-0.52339471274350047</v>
+        <v>-0.52364469626568799</v>
       </c>
       <c r="D148" s="10">
-        <v>-0.34487988032947975</v>
+        <v>-0.34939419150176071</v>
       </c>
     </row>
     <row r="149">
@@ -2645,10 +2645,10 @@
         <v>-0.018420426709712182</v>
       </c>
       <c r="C149" s="10">
-        <v>-1.0455113523708792</v>
+        <v>-1.0506989769072927</v>
       </c>
       <c r="D149" s="10">
-        <v>0.77348480197599601</v>
+        <v>0.77980092623457919</v>
       </c>
     </row>
     <row r="150">
@@ -2659,10 +2659,10 @@
         <v>-0.029178932240550084</v>
       </c>
       <c r="C150" s="10">
-        <v>-0.66586820962750792</v>
+        <v>-0.66745424632972306</v>
       </c>
       <c r="D150" s="10">
-        <v>-0.071078044655604036</v>
+        <v>-0.07296656106248571</v>
       </c>
     </row>
     <row r="151">
@@ -2673,10 +2673,10 @@
         <v>-0.0028180175646509769</v>
       </c>
       <c r="C151" s="10">
-        <v>0.12926283904510244</v>
+        <v>0.13464537931389373</v>
       </c>
       <c r="D151" s="10">
-        <v>-0.24647460066273313</v>
+        <v>-0.24880782421149697</v>
       </c>
     </row>
     <row r="152">
@@ -2687,10 +2687,10 @@
         <v>-0.030591883058950681</v>
       </c>
       <c r="C152" s="10">
-        <v>-1.3420876368804482</v>
+        <v>-1.3498469826644357</v>
       </c>
       <c r="D152" s="10">
-        <v>0.76267403946620793</v>
+        <v>0.76835522633297637</v>
       </c>
     </row>
     <row r="153">
@@ -2701,10 +2701,10 @@
         <v>0.0023310721753107251</v>
       </c>
       <c r="C153" s="10">
-        <v>1.4540961680828317</v>
+        <v>1.4715453290563079</v>
       </c>
       <c r="D153" s="10">
-        <v>-1.8023485244508142</v>
+        <v>-1.8186970205674127</v>
       </c>
     </row>
     <row r="154">
@@ -2715,10 +2715,10 @@
         <v>-0.0025773682414245787</v>
       </c>
       <c r="C154" s="10">
-        <v>-1.1719473009711658</v>
+        <v>-1.1784784874426997</v>
       </c>
       <c r="D154" s="10">
-        <v>1.4543184383914582</v>
+        <v>1.4675643757853378</v>
       </c>
     </row>
     <row r="155">
@@ -2729,10 +2729,10 @@
         <v>0.014555339163705654</v>
       </c>
       <c r="C155" s="10">
-        <v>1.4795241360552762</v>
+        <v>1.4970623849283682</v>
       </c>
       <c r="D155" s="10">
-        <v>-1.4370368889445637</v>
+        <v>-1.4495031244441499</v>
       </c>
     </row>
     <row r="156">
@@ -2743,10 +2743,10 @@
         <v>-0.02488712945019643</v>
       </c>
       <c r="C156" s="10">
-        <v>-0.83407715025870222</v>
+        <v>-0.83725336431142539</v>
       </c>
       <c r="D156" s="10">
-        <v>0.2876435555011857</v>
+        <v>0.28922766468986666</v>
       </c>
     </row>
     <row r="157">
@@ -2757,10 +2757,10 @@
         <v>0.010035620878801655</v>
       </c>
       <c r="C157" s="10">
-        <v>0.023291227973180235</v>
+        <v>0.027552665663564631</v>
       </c>
       <c r="D157" s="10">
-        <v>0.3103070650392164</v>
+        <v>0.31363647778327863</v>
       </c>
     </row>
     <row r="158">
@@ -2771,10 +2771,10 @@
         <v>0.010831700227979017</v>
       </c>
       <c r="C158" s="10">
-        <v>-0.16505633218744767</v>
+        <v>-0.16252832952119053</v>
       </c>
       <c r="D158" s="10">
-        <v>0.58130282727642146</v>
+        <v>0.58714791217118356</v>
       </c>
     </row>
     <row r="159">
@@ -2785,10 +2785,10 @@
         <v>0.010667112582245524</v>
       </c>
       <c r="C159" s="10">
-        <v>0.48558713625155953</v>
+        <v>0.49407287400068051</v>
       </c>
       <c r="D159" s="10">
-        <v>-0.27058620337258271</v>
+        <v>-0.27254631011325259</v>
       </c>
     </row>
     <row r="160">
@@ -2799,10 +2799,10 @@
         <v>0.0011985405149100739</v>
       </c>
       <c r="C160" s="10">
-        <v>-0.11737531687787729</v>
+        <v>-0.11429763717557555</v>
       </c>
       <c r="D160" s="10">
-        <v>0.20531761419204084</v>
+        <v>0.2072968369214595</v>
       </c>
     </row>
     <row r="161">
@@ -2813,10 +2813,10 @@
         <v>-0.0039387676433037125</v>
       </c>
       <c r="C161" s="10">
-        <v>-1.045880698491519</v>
+        <v>-1.0512419074438937</v>
       </c>
       <c r="D161" s="10">
-        <v>1.2459297686744804</v>
+        <v>1.2572082267209441</v>
       </c>
     </row>
     <row r="162">
@@ -2827,10 +2827,10 @@
         <v>-0.046017840100127244</v>
       </c>
       <c r="C162" s="10">
-        <v>-2.2624019631267074</v>
+        <v>-2.2784042961222082</v>
       </c>
       <c r="D162" s="10">
-        <v>1.4573170021667938</v>
+        <v>1.4686774551595727</v>
       </c>
     </row>
     <row r="163">
@@ -2841,10 +2841,10 @@
         <v>0.10332377603198248</v>
       </c>
       <c r="C163" s="10">
-        <v>3.7578514028247709</v>
+        <v>3.7952014964142995</v>
       </c>
       <c r="D163" s="10">
-        <v>-1.5082660974634032</v>
+        <v>-1.5174753625012174</v>
       </c>
     </row>
     <row r="164">
@@ -2855,10 +2855,10 @@
         <v>-0.035501844322037332</v>
       </c>
       <c r="C164" s="10">
-        <v>-0.15761988989711195</v>
+        <v>-0.15447925616804822</v>
       </c>
       <c r="D164" s="10">
-        <v>-0.93840553232658142</v>
+        <v>-0.94851174574469799</v>
       </c>
     </row>
     <row r="165">
@@ -2869,10 +2869,10 @@
         <v>0.10182069700358364</v>
       </c>
       <c r="C165" s="10">
-        <v>-0.24481467383228939</v>
+        <v>-0.24408615316701451</v>
       </c>
       <c r="D165" s="10">
-        <v>3.650449446080581</v>
+        <v>3.6883953704363122</v>
       </c>
     </row>
     <row r="166">
@@ -2883,10 +2883,10 @@
         <v>0.0065639670175053882</v>
       </c>
       <c r="C166" s="10">
-        <v>0.35396495564219771</v>
+        <v>0.36129408674885977</v>
       </c>
       <c r="D166" s="10">
-        <v>-0.23306162409023917</v>
+        <v>-0.23485892673091965</v>
       </c>
     </row>
     <row r="167">
@@ -2897,10 +2897,10 @@
         <v>-0.0050788630071737619</v>
       </c>
       <c r="C167" s="10">
-        <v>0.055197724811716149</v>
+        <v>0.05992886642000541</v>
       </c>
       <c r="D167" s="10">
-        <v>-0.22379364469526974</v>
+        <v>-0.2260188113365009</v>
       </c>
     </row>
     <row r="168">
@@ -2911,10 +2911,10 @@
         <v>-0.0016712054546177638</v>
       </c>
       <c r="C168" s="10">
-        <v>-0.42278088568718941</v>
+        <v>-0.42246507130880451</v>
       </c>
       <c r="D168" s="10">
-        <v>0.50914160289634169</v>
+        <v>0.51377557054269363</v>
       </c>
     </row>
     <row r="169">
@@ -2925,10 +2925,10 @@
         <v>0.016572489242439422</v>
       </c>
       <c r="C169" s="10">
-        <v>0.94536597883025464</v>
+        <v>0.95799099196746729</v>
       </c>
       <c r="D169" s="10">
-        <v>-0.67632610562279394</v>
+        <v>-0.6817401896713694</v>
       </c>
     </row>
     <row r="170">
@@ -2939,10 +2939,10 @@
         <v>-0.0098160923382861285</v>
       </c>
       <c r="C170" s="10">
-        <v>-0.23019142872524892</v>
+        <v>-0.2280169794012748</v>
       </c>
       <c r="D170" s="10">
-        <v>-0.0068743834453391583</v>
+        <v>-0.007322541687208751</v>
       </c>
     </row>
     <row r="171">
@@ -2953,10 +2953,10 @@
         <v>-0.0088453581177717587</v>
       </c>
       <c r="C171" s="10">
-        <v>-0.77673205292741787</v>
+        <v>-0.77957188626488538</v>
       </c>
       <c r="D171" s="10">
-        <v>0.73584350045289315</v>
+        <v>0.74223671223089349</v>
       </c>
     </row>
     <row r="172">
@@ -2967,10 +2967,10 @@
         <v>-0.012050286370239562</v>
       </c>
       <c r="C172" s="10">
-        <v>-0.40319831817221757</v>
+        <v>-0.40258126491720525</v>
       </c>
       <c r="D172" s="10">
-        <v>0.14540416587216418</v>
+        <v>0.14625153674964494</v>
       </c>
     </row>
     <row r="173">
@@ -2981,10 +2981,10 @@
         <v>-0.0040368504999854235</v>
       </c>
       <c r="C173" s="10">
-        <v>-0.43186874565651667</v>
+        <v>-0.4316083153769672</v>
       </c>
       <c r="D173" s="10">
-        <v>0.44386789673868804</v>
+        <v>0.44780019502441809</v>
       </c>
     </row>
     <row r="174">
@@ -2995,10 +2995,10 @@
         <v>-0.013466324687057357</v>
       </c>
       <c r="C174" s="10">
-        <v>-0.53787071112643992</v>
+        <v>-0.53846976694969551</v>
       </c>
       <c r="D174" s="10">
-        <v>0.27447140221500976</v>
+        <v>0.27643786069246351</v>
       </c>
     </row>
     <row r="175">
@@ -3009,10 +3009,10 @@
         <v>-0.0211137078970321</v>
       </c>
       <c r="C175" s="10">
-        <v>-0.22109775756528735</v>
+        <v>-0.2187072860897942</v>
       </c>
       <c r="D175" s="10">
-        <v>-0.38690065353123348</v>
+        <v>-0.39132496010513718</v>
       </c>
     </row>
     <row r="176">
@@ -3023,10 +3023,10 @@
         <v>-0.017406589907460791</v>
       </c>
       <c r="C176" s="10">
-        <v>-0.14099191198556887</v>
+        <v>-0.13791174485561325</v>
       </c>
       <c r="D176" s="10">
-        <v>-0.37030621565426552</v>
+        <v>-0.3744153759770017</v>
       </c>
     </row>
     <row r="177">
@@ -3037,10 +3037,10 @@
         <v>-0.010693521961778758</v>
       </c>
       <c r="C177" s="10">
-        <v>-0.56423001254355465</v>
+        <v>-0.56510294259290117</v>
       </c>
       <c r="D177" s="10">
-        <v>0.39913339935218395</v>
+        <v>0.40236307977782176</v>
       </c>
     </row>
     <row r="178">
@@ -3051,10 +3051,10 @@
         <v>-0.018722543255362153</v>
       </c>
       <c r="C178" s="10">
-        <v>-0.55532815338074037</v>
+        <v>-0.55602523299129836</v>
       </c>
       <c r="D178" s="10">
-        <v>0.12588179030216229</v>
+        <v>0.12625664141917867</v>
       </c>
     </row>
     <row r="179">
@@ -3065,10 +3065,10 @@
         <v>0.0016520092492235726</v>
       </c>
       <c r="C179" s="10">
-        <v>-0.12890826782544301</v>
+        <v>-0.12594148703130842</v>
       </c>
       <c r="D179" s="10">
-        <v>0.23510142507043716</v>
+        <v>0.23737324894545583</v>
       </c>
     </row>
     <row r="180">
@@ -3079,10 +3079,10 @@
         <v>0.015933538065822914</v>
       </c>
       <c r="C180" s="10">
-        <v>0.72753742333870464</v>
+        <v>0.73817600698513564</v>
       </c>
       <c r="D180" s="10">
-        <v>-0.41374220588403765</v>
+        <v>-0.41678081011948637</v>
       </c>
     </row>
     <row r="181">
@@ -3093,10 +3093,10 @@
         <v>-0.025806680711294876</v>
       </c>
       <c r="C181" s="10">
-        <v>-1.198422689141829</v>
+        <v>-1.2049232085441344</v>
       </c>
       <c r="D181" s="10">
-        <v>0.73170968655706392</v>
+        <v>0.73731815458439132</v>
       </c>
     </row>
     <row r="182">
@@ -3107,10 +3107,10 @@
         <v>-0.0094015456954362302</v>
       </c>
       <c r="C182" s="10">
-        <v>0.1404947704967873</v>
+        <v>0.1460575010669363</v>
       </c>
       <c r="D182" s="10">
-        <v>-0.47564843288919051</v>
+        <v>-0.48036935729450281</v>
       </c>
     </row>
     <row r="183">
@@ -3121,10 +3121,10 @@
         <v>-0.03246479304695829</v>
       </c>
       <c r="C183" s="10">
-        <v>-1.3662438990649957</v>
+        <v>-1.374202351845164</v>
       </c>
       <c r="D183" s="10">
-        <v>0.73306368102120656</v>
+        <v>0.73839134836025888</v>
       </c>
     </row>
     <row r="184">
@@ -3135,10 +3135,10 @@
         <v>-0.0044405481302150661</v>
       </c>
       <c r="C184" s="10">
-        <v>-0.28826855299912507</v>
+        <v>-0.28668890373411587</v>
       </c>
       <c r="D184" s="10">
-        <v>0.2438789792987355</v>
+        <v>0.24596286020664959</v>
       </c>
     </row>
     <row r="185">
@@ -3149,10 +3149,10 @@
         <v>0.0095715874442144147</v>
       </c>
       <c r="C185" s="10">
-        <v>0.27955943586788934</v>
+        <v>0.2861721318468583</v>
       </c>
       <c r="D185" s="10">
-        <v>-0.038235874310089082</v>
+        <v>-0.038117356094243368</v>
       </c>
     </row>
     <row r="186">
@@ -3163,10 +3163,10 @@
         <v>-0.0082433614785114087</v>
       </c>
       <c r="C186" s="10">
-        <v>0.37949637165472588</v>
+        <v>0.38723324103763673</v>
       </c>
       <c r="D186" s="10">
-        <v>-0.74885763650694948</v>
+        <v>-0.75602843686043564</v>
       </c>
     </row>
     <row r="187">
@@ -3177,10 +3177,10 @@
         <v>-0.015786929615702636</v>
       </c>
       <c r="C187" s="10">
-        <v>-0.14505065407327783</v>
+        <v>-0.14202667541887679</v>
       </c>
       <c r="D187" s="10">
-        <v>-0.3122400265134283</v>
+        <v>-0.31574634296009413</v>
       </c>
     </row>
     <row r="188">
@@ -3191,10 +3191,10 @@
         <v>-0.0059636743667435144</v>
       </c>
       <c r="C188" s="10">
-        <v>0.46062369485216398</v>
+        <v>0.46907638685121933</v>
       </c>
       <c r="D188" s="10">
-        <v>-0.78011287824072029</v>
+        <v>-0.78746939230819701</v>
       </c>
     </row>
     <row r="189">
@@ -3205,10 +3205,10 @@
         <v>-0.020123453126231688</v>
       </c>
       <c r="C189" s="10">
-        <v>0.018650445551403744</v>
+        <v>0.023223863698013627</v>
       </c>
       <c r="D189" s="10">
-        <v>-0.66655413341111525</v>
+        <v>-0.67349469985366484</v>
       </c>
     </row>
     <row r="190">
@@ -3219,10 +3219,10 @@
         <v>-0.0082303104388894918</v>
       </c>
       <c r="C190" s="10">
-        <v>-0.19974285919427326</v>
+        <v>-0.19730833029845857</v>
       </c>
       <c r="D190" s="10">
-        <v>0.0051916704470534895</v>
+        <v>0.004923792390764673</v>
       </c>
     </row>
     <row r="191">
@@ -3233,10 +3233,10 @@
         <v>0.033023868755983649</v>
       </c>
       <c r="C191" s="10">
-        <v>0.80895498495471707</v>
+        <v>0.82013797787758735</v>
       </c>
       <c r="D191" s="10">
-        <v>0.037311129020559899</v>
+        <v>0.039153920538886673</v>
       </c>
     </row>
     <row r="192">
@@ -3247,10 +3247,10 @@
         <v>0.024818673944070144</v>
       </c>
       <c r="C192" s="10">
-        <v>1.2694414567933634</v>
+        <v>1.2849360446579299</v>
       </c>
       <c r="D192" s="10">
-        <v>-0.82921993789805082</v>
+        <v>-0.83567044085951847</v>
       </c>
     </row>
     <row r="193">
@@ -3261,10 +3261,10 @@
         <v>0.056557170369929612</v>
       </c>
       <c r="C193" s="10">
-        <v>0.50600447589961473</v>
+        <v>0.51413776030569414</v>
       </c>
       <c r="D193" s="10">
-        <v>1.1984293113079563</v>
+        <v>1.2119369460942495</v>
       </c>
     </row>
     <row r="194">
@@ -3275,10 +3275,10 @@
         <v>-0.005100818301955674</v>
       </c>
       <c r="C194" s="10">
-        <v>-0.0090247487746710556</v>
+        <v>-0.0048812229302308691</v>
       </c>
       <c r="D194" s="10">
-        <v>-0.14095200093759325</v>
+        <v>-0.14241982613355694</v>
       </c>
     </row>
     <row r="195">
@@ -3289,10 +3289,10 @@
         <v>0.014029629615530521</v>
       </c>
       <c r="C195" s="10">
-        <v>-0.49570289552236713</v>
+        <v>-0.49623912052309443</v>
       </c>
       <c r="D195" s="10">
-        <v>1.1157153581500245</v>
+        <v>1.1265931227133543</v>
       </c>
     </row>
     <row r="196">
@@ -3303,10 +3303,10 @@
         <v>-0.014720414260141821</v>
       </c>
       <c r="C196" s="10">
-        <v>-0.068989067181007654</v>
+        <v>-0.065281377727076789</v>
       </c>
       <c r="D196" s="10">
-        <v>-0.37644231743872969</v>
+        <v>-0.38048935817480173</v>
       </c>
     </row>
     <row r="197">
@@ -3317,10 +3317,10 @@
         <v>-0.0023922606811444952</v>
       </c>
       <c r="C197" s="10">
-        <v>2.7230373703083015</v>
+        <v>2.7521575627327337</v>
       </c>
       <c r="D197" s="10">
-        <v>-3.6072506682066661</v>
+        <v>-3.6403287078564786</v>
       </c>
     </row>
     <row r="198">
@@ -3331,10 +3331,10 @@
         <v>-0.0030697918636610373</v>
       </c>
       <c r="C198" s="10">
-        <v>1.5649701691814435</v>
+        <v>1.5834977150214913</v>
       </c>
       <c r="D198" s="10">
-        <v>-2.1226188839886615</v>
+        <v>-2.1421368725596395</v>
       </c>
     </row>
     <row r="199">
@@ -3345,10 +3345,10 @@
         <v>0.0054621559732876551</v>
       </c>
       <c r="C199" s="10">
-        <v>-0.10557087084996104</v>
+        <v>-0.10243524713542054</v>
       </c>
       <c r="D199" s="10">
-        <v>0.32891267745416691</v>
+        <v>0.33221100473953619</v>
       </c>
     </row>
     <row r="200">
@@ -3359,10 +3359,10 @@
         <v>-0.0086068116285109818</v>
       </c>
       <c r="C200" s="10">
-        <v>-0.45531434757359285</v>
+        <v>-0.45521482056128537</v>
       </c>
       <c r="D200" s="10">
-        <v>0.3254346983386685</v>
+        <v>0.32808165212332879</v>
       </c>
     </row>
     <row r="201">
@@ -3373,10 +3373,10 @@
         <v>0.0080699506074671887</v>
       </c>
       <c r="C201" s="10">
-        <v>-0.2972237018970782</v>
+        <v>-0.29587306185660867</v>
       </c>
       <c r="D201" s="10">
-        <v>0.66325348607095147</v>
+        <v>0.66972710778328459</v>
       </c>
     </row>
     <row r="202">
@@ -3387,10 +3387,10 @@
         <v>-0.005923072898620668</v>
       </c>
       <c r="C202" s="10">
-        <v>-0.91925478567150942</v>
+        <v>-0.92343357630300016</v>
       </c>
       <c r="D202" s="10">
-        <v>1.0165125940302995</v>
+        <v>1.0256036538174165</v>
       </c>
     </row>
     <row r="203">
@@ -3401,10 +3401,10 @@
         <v>0.022047373105746546</v>
       </c>
       <c r="C203" s="10">
-        <v>0.58960690582930309</v>
+        <v>0.59891105756643259</v>
       </c>
       <c r="D203" s="10">
-        <v>-0.035033665780904527</v>
+        <v>-0.034336455298984901</v>
       </c>
     </row>
     <row r="204">
@@ -3415,10 +3415,10 @@
         <v>-0.016414945848942389</v>
       </c>
       <c r="C204" s="10">
-        <v>0.1730781664045386</v>
+        <v>0.17902158466211293</v>
       </c>
       <c r="D204" s="10">
-        <v>-0.74661150528597753</v>
+        <v>-0.75412158679600449</v>
       </c>
     </row>
     <row r="205">
@@ -3429,10 +3429,10 @@
         <v>-0.0080168081610074646</v>
       </c>
       <c r="C205" s="10">
-        <v>-0.39760612408068857</v>
+        <v>-0.39698528714460984</v>
       </c>
       <c r="D205" s="10">
-        <v>0.26958144394414973</v>
+        <v>0.27174311454319672</v>
       </c>
     </row>
     <row r="206">
@@ -3443,10 +3443,10 @@
         <v>-0.011201002679241137</v>
       </c>
       <c r="C206" s="10">
-        <v>-0.038619965247823296</v>
+        <v>-0.034675649673734356</v>
       </c>
       <c r="D206" s="10">
-        <v>-0.30125492464381443</v>
+        <v>-0.30445874208306978</v>
       </c>
     </row>
     <row r="207">
@@ -3457,10 +3457,10 @@
         <v>-0.0091207421799714868</v>
       </c>
       <c r="C207" s="10">
-        <v>-0.72467383049270173</v>
+        <v>-0.72703390143446411</v>
       </c>
       <c r="D207" s="10">
-        <v>0.65913781914956227</v>
+        <v>0.66481676274210011</v>
       </c>
     </row>
     <row r="208">
@@ -3471,10 +3471,10 @@
         <v>0.0084395042520943563</v>
       </c>
       <c r="C208" s="10">
-        <v>0.11910533155350854</v>
+        <v>0.12426258284644394</v>
       </c>
       <c r="D208" s="10">
-        <v>0.13362910756904728</v>
+        <v>0.13527097564180848</v>
       </c>
     </row>
     <row r="209">
@@ -3485,10 +3485,10 @@
         <v>-0.0085309369329932012</v>
       </c>
       <c r="C209" s="10">
-        <v>-0.86459784024804009</v>
+        <v>-0.86824566679881909</v>
       </c>
       <c r="D209" s="10">
-        <v>0.86040914778338073</v>
+        <v>0.86795644295461749</v>
       </c>
     </row>
     <row r="210">
@@ -3499,10 +3499,10 @@
         <v>0.042255738611461889</v>
       </c>
       <c r="C210" s="10">
-        <v>0.77017664678943343</v>
+        <v>0.78089617156417002</v>
       </c>
       <c r="D210" s="10">
-        <v>0.38863520597897727</v>
+        <v>0.39410044772302277</v>
       </c>
     </row>
     <row r="211">
@@ -3513,10 +3513,10 @@
         <v>-0.014835292571359442</v>
       </c>
       <c r="C211" s="10">
-        <v>0.26276736291668212</v>
+        <v>0.26951320420951658</v>
       </c>
       <c r="D211" s="10">
-        <v>-0.81182069135730406</v>
+        <v>-0.81985811758447658</v>
       </c>
     </row>
     <row r="212">
@@ -3527,10 +3527,10 @@
         <v>0.090195315811054722</v>
       </c>
       <c r="C212" s="10">
-        <v>1.9621232018076609</v>
+        <v>1.9831900221449914</v>
       </c>
       <c r="D212" s="10">
-        <v>0.40021784648834163</v>
+        <v>0.40790016606298629</v>
       </c>
     </row>
     <row r="213">
@@ -3541,10 +3541,10 @@
         <v>0.11921370594555686</v>
       </c>
       <c r="C213" s="10">
-        <v>1.7664455906396748</v>
+        <v>1.785380180833444</v>
       </c>
       <c r="D213" s="10">
-        <v>1.6005294880124201</v>
+        <v>1.6204769561705357</v>
       </c>
     </row>
     <row r="214">
@@ -3555,10 +3555,10 @@
         <v>-0.045125793550790362</v>
       </c>
       <c r="C214" s="10">
-        <v>-0.80034758952640239</v>
+        <v>-0.80297718716677324</v>
       </c>
       <c r="D214" s="10">
-        <v>-0.41582863210426491</v>
+        <v>-0.42157512640159811</v>
       </c>
     </row>
     <row r="215">
@@ -3569,10 +3569,10 @@
         <v>0.076083891136199081</v>
       </c>
       <c r="C215" s="10">
-        <v>2.1179859948797661</v>
+        <v>2.1406453899473967</v>
       </c>
       <c r="D215" s="10">
-        <v>-0.26246702693261398</v>
+        <v>-0.26147213826847976</v>
       </c>
     </row>
     <row r="216">
@@ -3583,10 +3583,10 @@
         <v>0.027148287752088551</v>
       </c>
       <c r="C216" s="10">
-        <v>0.031510002562078691</v>
+        <v>0.035645546648452951</v>
       </c>
       <c r="D216" s="10">
-        <v>0.85732423131238833</v>
+        <v>0.86641444834341452</v>
       </c>
     </row>
     <row r="217">
@@ -3597,10 +3597,10 @@
         <v>0.10762162787246246</v>
       </c>
       <c r="C217" s="10">
-        <v>1.465711557497027</v>
+        <v>1.482029558167534</v>
       </c>
       <c r="D217" s="10">
-        <v>1.6140104229220009</v>
+        <v>1.6335708261451054</v>
       </c>
     </row>
     <row r="218">
@@ -3611,10 +3611,10 @@
         <v>-0.17188825558458773</v>
       </c>
       <c r="C218" s="10">
-        <v>-2.7553356437467666</v>
+        <v>-2.7743707878641031</v>
       </c>
       <c r="D218" s="10">
-        <v>-2.0035266234210334</v>
+        <v>-2.0293885184545819</v>
       </c>
     </row>
     <row r="219">
@@ -3625,10 +3625,10 @@
         <v>0.2611012424548031</v>
       </c>
       <c r="C219" s="10">
-        <v>4.9228583828024819</v>
+        <v>4.9690182457477459</v>
       </c>
       <c r="D219" s="10">
-        <v>2.1180375910745108</v>
+        <v>2.1489702971610054</v>
       </c>
     </row>
     <row r="220">
@@ -3639,10 +3639,10 @@
         <v>-0.09302201824562073</v>
       </c>
       <c r="C220" s="10">
-        <v>-1.4828892974373844</v>
+        <v>-1.4912037566616823</v>
       </c>
       <c r="D220" s="10">
-        <v>-1.0887637606352119</v>
+        <v>-1.1027792516260881</v>
       </c>
     </row>
     <row r="221">
@@ -3653,10 +3653,10 @@
         <v>0.031463289945068161</v>
       </c>
       <c r="C221" s="10">
-        <v>-0.83371412383080634</v>
+        <v>-0.83754930362117685</v>
       </c>
       <c r="D221" s="10">
-        <v>2.1236592537573316</v>
+        <v>2.1445311467264898</v>
       </c>
     </row>
     <row r="222">
@@ -3667,10 +3667,10 @@
         <v>-0.079943752323201819</v>
       </c>
       <c r="C222" s="10">
-        <v>-1.5808516994034867</v>
+        <v>-1.5902165872962666</v>
       </c>
       <c r="D222" s="10">
-        <v>-0.53508182178639796</v>
+        <v>-0.54345315884825662</v>
       </c>
     </row>
     <row r="223">
@@ -3681,10 +3681,10 @@
         <v>-0.029740686356060839</v>
       </c>
       <c r="C223" s="10">
-        <v>-0.48517727551272827</v>
+        <v>-0.48510271774810837</v>
       </c>
       <c r="D223" s="10">
-        <v>-0.32447531540916369</v>
+        <v>-0.32870809382488009</v>
       </c>
     </row>
     <row r="224">
@@ -3695,10 +3695,10 @@
         <v>-0.058129683979852409</v>
       </c>
       <c r="C224" s="10">
-        <v>-0.99539433808284339</v>
+        <v>-0.99965650155817909</v>
       </c>
       <c r="D224" s="10">
-        <v>-0.58586467077888282</v>
+        <v>-0.59374026107183742</v>
       </c>
     </row>
     <row r="225">
@@ -3709,10 +3709,10 @@
         <v>-0.0048533831339413417</v>
       </c>
       <c r="C225" s="10">
-        <v>-0.95041181066409419</v>
+        <v>-0.95488837572893293</v>
       </c>
       <c r="D225" s="10">
-        <v>1.0919114158260683</v>
+        <v>1.1017397590097335</v>
       </c>
     </row>
     <row r="226">
@@ -3723,10 +3723,10 @@
         <v>-0.059713449426662388</v>
       </c>
       <c r="C226" s="10">
-        <v>-1.1090828201134517</v>
+        <v>-1.1143670407585071</v>
       </c>
       <c r="D226" s="10">
-        <v>-0.48956503445136801</v>
+        <v>-0.49662886818928842</v>
       </c>
     </row>
     <row r="227">
@@ -3737,10 +3737,10 @@
         <v>0.044565364544650626</v>
       </c>
       <c r="C227" s="10">
-        <v>1.0661042382792314</v>
+        <v>1.07950545284951</v>
       </c>
       <c r="D227" s="10">
-        <v>0.078888028849837935</v>
+        <v>0.081619641248331834</v>
       </c>
     </row>
     <row r="228">
@@ -3751,10 +3751,10 @@
         <v>-0.11665143178482844</v>
       </c>
       <c r="C228" s="10">
-        <v>-1.7220824327155833</v>
+        <v>-1.7323086787260968</v>
       </c>
       <c r="D228" s="10">
-        <v>-1.5476538289919921</v>
+        <v>-1.5669104041206545</v>
       </c>
     </row>
     <row r="229">
@@ -3765,10 +3765,10 @@
         <v>-0.021170418527530436</v>
       </c>
       <c r="C229" s="10">
-        <v>-1.1009756595430393</v>
+        <v>-1.1066386674161086</v>
       </c>
       <c r="D229" s="10">
-        <v>0.75602350276425223</v>
+        <v>0.76205869351410016</v>
       </c>
     </row>
     <row r="230">
@@ -3779,10 +3779,10 @@
         <v>-0.012761208217025687</v>
       </c>
       <c r="C230" s="10">
-        <v>-0.48805972859141278</v>
+        <v>-0.4882111164607546</v>
       </c>
       <c r="D230" s="10">
-        <v>0.23264450778700863</v>
+        <v>0.23425914537369374</v>
       </c>
     </row>
     <row r="231">
@@ -3793,10 +3793,10 @@
         <v>0.042993296087479836</v>
       </c>
       <c r="C231" s="10">
-        <v>0.64176204105922963</v>
+        <v>0.65129742741696595</v>
       </c>
       <c r="D231" s="10">
-        <v>0.57974744797393341</v>
+        <v>0.58699455435402081</v>
       </c>
     </row>
     <row r="232">
@@ -3807,10 +3807,10 @@
         <v>-0.048412118036576961</v>
       </c>
       <c r="C232" s="10">
-        <v>-0.64639457851451587</v>
+        <v>-0.64757631085666123</v>
       </c>
       <c r="D232" s="10">
-        <v>-0.72323340287713078</v>
+        <v>-0.73193850651099379</v>
       </c>
     </row>
     <row r="233">
@@ -3821,10 +3821,10 @@
         <v>0.010904863996432345</v>
       </c>
       <c r="C233" s="10">
-        <v>0.79182002083275538</v>
+        <v>0.8031061308525228</v>
       </c>
       <c r="D233" s="10">
-        <v>-0.66126458137349164</v>
+        <v>-0.66679037456737811</v>
       </c>
     </row>
     <row r="234">
@@ -3835,10 +3835,10 @@
         <v>-0.024746492881667397</v>
       </c>
       <c r="C234" s="10">
-        <v>-0.297609006375531</v>
+        <v>-0.2958762003021681</v>
       </c>
       <c r="D234" s="10">
-        <v>-0.40574932174387329</v>
+        <v>-0.41050613582917017</v>
       </c>
     </row>
     <row r="235">
@@ -3849,10 +3849,10 @@
         <v>0.039313869398462722</v>
       </c>
       <c r="C235" s="10">
-        <v>0.073527623005261569</v>
+        <v>0.077904801566067286</v>
       </c>
       <c r="D235" s="10">
-        <v>1.1991391786772516</v>
+        <v>1.2118939902390564</v>
       </c>
     </row>
     <row r="236">
@@ -3863,10 +3863,10 @@
         <v>-0.027512954439456096</v>
       </c>
       <c r="C236" s="10">
-        <v>-0.55531143856357434</v>
+        <v>-0.55590505111065991</v>
       </c>
       <c r="D236" s="10">
-        <v>-0.16062380140712876</v>
+        <v>-0.16325863104377905</v>
       </c>
     </row>
     <row r="237">
@@ -3877,10 +3877,10 @@
         <v>0.067888653805241631</v>
       </c>
       <c r="C237" s="10">
-        <v>0.4192152478632703</v>
+        <v>0.42642090958431855</v>
       </c>
       <c r="D237" s="10">
-        <v>1.6806457957612777</v>
+        <v>1.6990664897144654</v>
       </c>
     </row>
     <row r="238">
@@ -3891,10 +3891,10 @@
         <v>-0.10225235100889243</v>
       </c>
       <c r="C238" s="10">
-        <v>-1.6569078741723882</v>
+        <v>-1.6667067642525795</v>
       </c>
       <c r="D238" s="10">
-        <v>-1.163176566031392</v>
+        <v>-1.1782796744879993</v>
       </c>
     </row>
     <row r="239">
@@ -3905,10 +3905,10 @@
         <v>0.073762289590499908</v>
       </c>
       <c r="C239" s="10">
-        <v>1.0072757128310315</v>
+        <v>1.0197952755751463</v>
       </c>
       <c r="D239" s="10">
-        <v>1.1069695824339463</v>
+        <v>1.1203976613010844</v>
       </c>
     </row>
     <row r="240">
@@ -3919,10 +3919,10 @@
         <v>0.035900601209337371</v>
       </c>
       <c r="C240" s="10">
-        <v>0.67960928062502912</v>
+        <v>0.6895744703149993</v>
       </c>
       <c r="D240" s="10">
-        <v>0.29935155421255005</v>
+        <v>0.30371966639022951</v>
       </c>
     </row>
     <row r="241">
@@ -3933,10 +3933,10 @@
         <v>0.024945551389426199</v>
       </c>
       <c r="C241" s="10">
-        <v>-0.39725447072838066</v>
+        <v>-0.39701782281521175</v>
       </c>
       <c r="D241" s="10">
-        <v>1.3433835103837699</v>
+        <v>1.3568259733137014</v>
       </c>
     </row>
     <row r="242">
@@ -3947,10 +3947,94 @@
         <v>-0.012009670494132168</v>
       </c>
       <c r="C242" s="10">
-        <v>-0.5463142369356736</v>
+        <v>-0.54700770244938568</v>
       </c>
       <c r="D242" s="10">
-        <v>0.33293000097410258</v>
+        <v>0.33549571724025956</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="11">
+        <v>46009</v>
+      </c>
+      <c r="B243" s="10">
+        <v>0.010392132542960991</v>
+      </c>
+      <c r="C243" s="10">
+        <v>-0.23929229351071388</v>
+      </c>
+      <c r="D243" s="10">
+        <v>0.67255280240446758</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B244" s="10">
+        <v>0.016831626221716758</v>
+      </c>
+      <c r="C244" s="10">
+        <v>0.37410272803693928</v>
+      </c>
+      <c r="D244" s="10">
+        <v>0.086462597883546002</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="11">
+        <v>46100</v>
+      </c>
+      <c r="B245" s="10">
+        <v>-0.040924623738603505</v>
+      </c>
+      <c r="C245" s="10">
+        <v>-1.0496258011025781</v>
+      </c>
+      <c r="D245" s="10">
+        <v>0.037621351643109639</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B246" s="10">
+        <v>-0.028801543650667769</v>
+      </c>
+      <c r="C246" s="10">
+        <v>-0.44009375207772944</v>
+      </c>
+      <c r="D246" s="10">
+        <v>-0.35635309030732665</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="11">
+        <v>46184</v>
+      </c>
+      <c r="B247" s="10">
+        <v>-0.0040145760201480887</v>
+      </c>
+      <c r="C247" s="10">
+        <v>-0.1824833716908521</v>
+      </c>
+      <c r="D247" s="10">
+        <v>0.12440735888803481</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="11">
+        <v>46226</v>
+      </c>
+      <c r="B248" s="10">
+        <v>0.0030873283588550293</v>
+      </c>
+      <c r="C248" s="10">
+        <v>0.53216458404953415</v>
+      </c>
+      <c r="D248" s="10">
+        <v>-0.57161386317442808</v>
       </c>
     </row>
   </sheetData>
